--- a/OnlabSokFelevesLetszamStat/CourseAliases.xlsx
+++ b/OnlabSokFelevesLetszamStat/CourseAliases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_learning_ai\OnlabSokFelevesLetszamStat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AAF9107-6D61-4770-84B8-11B80E5842AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C511369-BCE7-4FC5-B4C6-E3981FC82F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-18120" windowWidth="29040" windowHeight="17640" xr2:uid="{A2403E9B-3DE4-472F-B269-6A96B12357E5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="116">
   <si>
     <t>CourseName</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>VIAUBB07</t>
+  </si>
+  <si>
+    <t>CoursesSemesterIndex</t>
   </si>
 </sst>
 </file>
@@ -763,14 +766,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B33EF2C-3696-4D09-9CC9-35CB795F091E}">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -780,8 +783,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -791,8 +797,11 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -802,8 +811,11 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -813,8 +825,11 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -824,8 +839,11 @@
       <c r="C5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -835,8 +853,11 @@
       <c r="C6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -846,8 +867,11 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -857,8 +881,11 @@
       <c r="C8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -868,8 +895,11 @@
       <c r="C9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -879,8 +909,11 @@
       <c r="C10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -890,8 +923,11 @@
       <c r="C11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -901,8 +937,11 @@
       <c r="C12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -912,8 +951,11 @@
       <c r="C13" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -923,8 +965,11 @@
       <c r="C14" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -934,8 +979,11 @@
       <c r="C15" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -945,8 +993,11 @@
       <c r="C16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -956,8 +1007,11 @@
       <c r="C17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -967,8 +1021,11 @@
       <c r="C18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -978,8 +1035,11 @@
       <c r="C19" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -989,8 +1049,11 @@
       <c r="C20" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1000,8 +1063,11 @@
       <c r="C21" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1011,8 +1077,11 @@
       <c r="C22" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -1022,8 +1091,11 @@
       <c r="C23" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1033,8 +1105,11 @@
       <c r="C24" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1044,8 +1119,11 @@
       <c r="C25" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1055,8 +1133,11 @@
       <c r="C26" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>57</v>
       </c>
@@ -1066,8 +1147,11 @@
       <c r="C27" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -1077,8 +1161,11 @@
       <c r="C28" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -1088,8 +1175,11 @@
       <c r="C29" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1099,8 +1189,11 @@
       <c r="C30" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1110,8 +1203,11 @@
       <c r="C31" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1121,8 +1217,11 @@
       <c r="C32" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1132,8 +1231,11 @@
       <c r="C33" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1143,8 +1245,11 @@
       <c r="C34" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>74</v>
       </c>
@@ -1154,8 +1259,11 @@
       <c r="C35" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>76</v>
       </c>
@@ -1165,8 +1273,11 @@
       <c r="C36" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -1176,8 +1287,11 @@
       <c r="C37" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>81</v>
       </c>
@@ -1187,8 +1301,11 @@
       <c r="C38" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>83</v>
       </c>
@@ -1198,8 +1315,11 @@
       <c r="C39" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>85</v>
       </c>
@@ -1209,8 +1329,11 @@
       <c r="C40" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>87</v>
       </c>
@@ -1220,8 +1343,11 @@
       <c r="C41" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>89</v>
       </c>
@@ -1231,8 +1357,11 @@
       <c r="C42" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>91</v>
       </c>
@@ -1242,8 +1371,11 @@
       <c r="C43" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>93</v>
       </c>
@@ -1253,8 +1385,11 @@
       <c r="C44" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>96</v>
       </c>
@@ -1264,8 +1399,11 @@
       <c r="C45" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -1275,8 +1413,11 @@
       <c r="C46" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -1286,8 +1427,11 @@
       <c r="C47" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>102</v>
       </c>
@@ -1297,8 +1441,11 @@
       <c r="C48" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -1308,8 +1455,11 @@
       <c r="C49" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>106</v>
       </c>
@@ -1319,8 +1469,11 @@
       <c r="C50" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>108</v>
       </c>
@@ -1330,8 +1483,11 @@
       <c r="C51" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>111</v>
       </c>
@@ -1341,8 +1497,11 @@
       <c r="C52" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>113</v>
       </c>
@@ -1351,6 +1510,9 @@
       </c>
       <c r="C53" t="s">
         <v>110</v>
+      </c>
+      <c r="D53">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
